--- a/src/test/resources/expected.xlsx
+++ b/src/test/resources/expected.xlsx
@@ -27,12 +27,228 @@
             <sz val="12.0"/>
             <rFont val="Calibri"/>
           </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
           <t>The default language does not need/have a translation for the quantity 'few'.
 If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B12" authorId="0">
+    <comment ref="B15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -44,7 +260,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C12" authorId="0">
+    <comment ref="C15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -56,7 +272,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D12" authorId="0">
+    <comment ref="D15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -68,7 +284,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E12" authorId="0">
+    <comment ref="E15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -80,7 +296,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F12" authorId="0">
+    <comment ref="F15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -92,7 +308,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G12" authorId="0">
+    <comment ref="G15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -104,7 +320,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H12" authorId="0">
+    <comment ref="H15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -116,7 +332,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I12" authorId="0">
+    <comment ref="I15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -128,7 +344,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A13" authorId="0">
+    <comment ref="A16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -140,7 +356,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B13" authorId="0">
+    <comment ref="B16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -152,7 +368,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C13" authorId="0">
+    <comment ref="C16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -164,7 +380,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D13" authorId="0">
+    <comment ref="D16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -176,7 +392,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E13" authorId="0">
+    <comment ref="E16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -188,7 +404,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F13" authorId="0">
+    <comment ref="F16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -200,7 +416,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G13" authorId="0">
+    <comment ref="G16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -212,7 +428,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H13" authorId="0">
+    <comment ref="H16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -224,7 +440,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I13" authorId="0">
+    <comment ref="I16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -236,7 +452,115 @@
         </r>
       </text>
     </comment>
-    <comment ref="A16" authorId="0">
+    <comment ref="A37" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B37" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C37" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D37" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E37" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F37" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G37" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H37" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I37" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A39" authorId="0">
       <text>
         <r>
           <rPr>
@@ -248,7 +572,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B16" authorId="0">
+    <comment ref="B39" authorId="0">
       <text>
         <r>
           <rPr>
@@ -260,7 +584,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C16" authorId="0">
+    <comment ref="C39" authorId="0">
       <text>
         <r>
           <rPr>
@@ -272,7 +596,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D16" authorId="0">
+    <comment ref="D39" authorId="0">
       <text>
         <r>
           <rPr>
@@ -284,7 +608,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E16" authorId="0">
+    <comment ref="E39" authorId="0">
       <text>
         <r>
           <rPr>
@@ -296,7 +620,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F16" authorId="0">
+    <comment ref="F39" authorId="0">
       <text>
         <r>
           <rPr>
@@ -308,7 +632,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G16" authorId="0">
+    <comment ref="G39" authorId="0">
       <text>
         <r>
           <rPr>
@@ -320,7 +644,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H16" authorId="0">
+    <comment ref="H39" authorId="0">
       <text>
         <r>
           <rPr>
@@ -332,7 +656,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I16" authorId="0">
+    <comment ref="I39" authorId="0">
       <text>
         <r>
           <rPr>
@@ -344,7 +668,223 @@
         </r>
       </text>
     </comment>
-    <comment ref="A17" authorId="0">
+    <comment ref="A40" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'few'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B40" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'few'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C40" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'few'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D40" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'few'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E40" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'few'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F40" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'few'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G40" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'few'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H40" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'few'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I40" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'few'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A41" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'many'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B41" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'many'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C41" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'many'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D41" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'many'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E41" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'many'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F41" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'many'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G41" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'many'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H41" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'many'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I41" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'many'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A43" authorId="0">
       <text>
         <r>
           <rPr>
@@ -356,7 +896,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B17" authorId="0">
+    <comment ref="B43" authorId="0">
       <text>
         <r>
           <rPr>
@@ -368,7 +908,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C17" authorId="0">
+    <comment ref="C43" authorId="0">
       <text>
         <r>
           <rPr>
@@ -380,7 +920,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D17" authorId="0">
+    <comment ref="D43" authorId="0">
       <text>
         <r>
           <rPr>
@@ -392,7 +932,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E17" authorId="0">
+    <comment ref="E43" authorId="0">
       <text>
         <r>
           <rPr>
@@ -404,7 +944,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F17" authorId="0">
+    <comment ref="F43" authorId="0">
       <text>
         <r>
           <rPr>
@@ -416,7 +956,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G17" authorId="0">
+    <comment ref="G43" authorId="0">
       <text>
         <r>
           <rPr>
@@ -428,7 +968,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H17" authorId="0">
+    <comment ref="H43" authorId="0">
       <text>
         <r>
           <rPr>
@@ -440,7 +980,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I17" authorId="0">
+    <comment ref="I43" authorId="0">
       <text>
         <r>
           <rPr>
@@ -452,7 +992,115 @@
         </r>
       </text>
     </comment>
-    <comment ref="A37" authorId="0">
+    <comment ref="A45" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B45" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C45" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D45" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E45" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F45" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G45" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H45" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I45" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A46" authorId="0">
       <text>
         <r>
           <rPr>
@@ -464,7 +1112,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B37" authorId="0">
+    <comment ref="B46" authorId="0">
       <text>
         <r>
           <rPr>
@@ -476,7 +1124,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C37" authorId="0">
+    <comment ref="C46" authorId="0">
       <text>
         <r>
           <rPr>
@@ -488,7 +1136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D37" authorId="0">
+    <comment ref="D46" authorId="0">
       <text>
         <r>
           <rPr>
@@ -500,7 +1148,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E37" authorId="0">
+    <comment ref="E46" authorId="0">
       <text>
         <r>
           <rPr>
@@ -512,7 +1160,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F37" authorId="0">
+    <comment ref="F46" authorId="0">
       <text>
         <r>
           <rPr>
@@ -524,7 +1172,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G37" authorId="0">
+    <comment ref="G46" authorId="0">
       <text>
         <r>
           <rPr>
@@ -536,7 +1184,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H37" authorId="0">
+    <comment ref="H46" authorId="0">
       <text>
         <r>
           <rPr>
@@ -548,7 +1196,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I37" authorId="0">
+    <comment ref="I46" authorId="0">
       <text>
         <r>
           <rPr>
@@ -560,7 +1208,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A38" authorId="0">
+    <comment ref="A47" authorId="0">
       <text>
         <r>
           <rPr>
@@ -572,7 +1220,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B38" authorId="0">
+    <comment ref="B47" authorId="0">
       <text>
         <r>
           <rPr>
@@ -584,7 +1232,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C38" authorId="0">
+    <comment ref="C47" authorId="0">
       <text>
         <r>
           <rPr>
@@ -596,7 +1244,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D38" authorId="0">
+    <comment ref="D47" authorId="0">
       <text>
         <r>
           <rPr>
@@ -608,7 +1256,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E38" authorId="0">
+    <comment ref="E47" authorId="0">
       <text>
         <r>
           <rPr>
@@ -620,7 +1268,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F38" authorId="0">
+    <comment ref="F47" authorId="0">
       <text>
         <r>
           <rPr>
@@ -632,7 +1280,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G38" authorId="0">
+    <comment ref="G47" authorId="0">
       <text>
         <r>
           <rPr>
@@ -644,7 +1292,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H38" authorId="0">
+    <comment ref="H47" authorId="0">
       <text>
         <r>
           <rPr>
@@ -656,7 +1304,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I38" authorId="0">
+    <comment ref="I47" authorId="0">
       <text>
         <r>
           <rPr>
@@ -668,7 +1316,115 @@
         </r>
       </text>
     </comment>
-    <comment ref="A41" authorId="0">
+    <comment ref="A91" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B91" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C91" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D91" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E91" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F91" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G91" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H91" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I91" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A93" authorId="0">
       <text>
         <r>
           <rPr>
@@ -680,7 +1436,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B41" authorId="0">
+    <comment ref="B93" authorId="0">
       <text>
         <r>
           <rPr>
@@ -692,7 +1448,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C41" authorId="0">
+    <comment ref="C93" authorId="0">
       <text>
         <r>
           <rPr>
@@ -704,7 +1460,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D41" authorId="0">
+    <comment ref="D93" authorId="0">
       <text>
         <r>
           <rPr>
@@ -716,7 +1472,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E41" authorId="0">
+    <comment ref="E93" authorId="0">
       <text>
         <r>
           <rPr>
@@ -728,7 +1484,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F41" authorId="0">
+    <comment ref="F93" authorId="0">
       <text>
         <r>
           <rPr>
@@ -740,7 +1496,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G41" authorId="0">
+    <comment ref="G93" authorId="0">
       <text>
         <r>
           <rPr>
@@ -752,7 +1508,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H41" authorId="0">
+    <comment ref="H93" authorId="0">
       <text>
         <r>
           <rPr>
@@ -764,7 +1520,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I41" authorId="0">
+    <comment ref="I93" authorId="0">
       <text>
         <r>
           <rPr>
@@ -776,7 +1532,223 @@
         </r>
       </text>
     </comment>
-    <comment ref="A42" authorId="0">
+    <comment ref="A94" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'few'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B94" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'few'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C94" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'few'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D94" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'few'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E94" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'few'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F94" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'few'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G94" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'few'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H94" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'few'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I94" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'few'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A95" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'many'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B95" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'many'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C95" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'many'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D95" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'many'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E95" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'many'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F95" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'many'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G95" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'many'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H95" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'many'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I95" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'many'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A147" authorId="0">
       <text>
         <r>
           <rPr>
@@ -788,7 +1760,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B42" authorId="0">
+    <comment ref="B147" authorId="0">
       <text>
         <r>
           <rPr>
@@ -800,7 +1772,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C42" authorId="0">
+    <comment ref="C147" authorId="0">
       <text>
         <r>
           <rPr>
@@ -812,7 +1784,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D42" authorId="0">
+    <comment ref="D147" authorId="0">
       <text>
         <r>
           <rPr>
@@ -824,7 +1796,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E42" authorId="0">
+    <comment ref="E147" authorId="0">
       <text>
         <r>
           <rPr>
@@ -836,7 +1808,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F42" authorId="0">
+    <comment ref="F147" authorId="0">
       <text>
         <r>
           <rPr>
@@ -848,7 +1820,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G42" authorId="0">
+    <comment ref="G147" authorId="0">
       <text>
         <r>
           <rPr>
@@ -860,7 +1832,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H42" authorId="0">
+    <comment ref="H147" authorId="0">
       <text>
         <r>
           <rPr>
@@ -872,7 +1844,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I42" authorId="0">
+    <comment ref="I147" authorId="0">
       <text>
         <r>
           <rPr>
@@ -884,7 +1856,115 @@
         </r>
       </text>
     </comment>
-    <comment ref="A43" authorId="0">
+    <comment ref="A149" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B149" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C149" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D149" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E149" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F149" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G149" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H149" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I149" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A150" authorId="0">
       <text>
         <r>
           <rPr>
@@ -896,7 +1976,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B43" authorId="0">
+    <comment ref="B150" authorId="0">
       <text>
         <r>
           <rPr>
@@ -908,7 +1988,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C43" authorId="0">
+    <comment ref="C150" authorId="0">
       <text>
         <r>
           <rPr>
@@ -920,7 +2000,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D43" authorId="0">
+    <comment ref="D150" authorId="0">
       <text>
         <r>
           <rPr>
@@ -932,7 +2012,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E43" authorId="0">
+    <comment ref="E150" authorId="0">
       <text>
         <r>
           <rPr>
@@ -944,7 +2024,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F43" authorId="0">
+    <comment ref="F150" authorId="0">
       <text>
         <r>
           <rPr>
@@ -956,7 +2036,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G43" authorId="0">
+    <comment ref="G150" authorId="0">
       <text>
         <r>
           <rPr>
@@ -968,7 +2048,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H43" authorId="0">
+    <comment ref="H150" authorId="0">
       <text>
         <r>
           <rPr>
@@ -980,7 +2060,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I43" authorId="0">
+    <comment ref="I150" authorId="0">
       <text>
         <r>
           <rPr>
@@ -992,7 +2072,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A44" authorId="0">
+    <comment ref="A151" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1004,7 +2084,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B44" authorId="0">
+    <comment ref="B151" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1016,7 +2096,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C44" authorId="0">
+    <comment ref="C151" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1028,7 +2108,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D44" authorId="0">
+    <comment ref="D151" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1040,7 +2120,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E44" authorId="0">
+    <comment ref="E151" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1052,7 +2132,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F44" authorId="0">
+    <comment ref="F151" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1064,7 +2144,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G44" authorId="0">
+    <comment ref="G151" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1076,7 +2156,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H44" authorId="0">
+    <comment ref="H151" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1088,7 +2168,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I44" authorId="0">
+    <comment ref="I151" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1100,7 +2180,115 @@
         </r>
       </text>
     </comment>
-    <comment ref="A47" authorId="0">
+    <comment ref="A190" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B190" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C190" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D190" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E190" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F190" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G190" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H190" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I190" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A192" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1112,7 +2300,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B47" authorId="0">
+    <comment ref="B192" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1124,7 +2312,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C47" authorId="0">
+    <comment ref="C192" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1136,7 +2324,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D47" authorId="0">
+    <comment ref="D192" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1148,7 +2336,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E47" authorId="0">
+    <comment ref="E192" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1160,7 +2348,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F47" authorId="0">
+    <comment ref="F192" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1172,7 +2360,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G47" authorId="0">
+    <comment ref="G192" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1184,7 +2372,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H47" authorId="0">
+    <comment ref="H192" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1196,7 +2384,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I47" authorId="0">
+    <comment ref="I192" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1208,7 +2396,223 @@
         </r>
       </text>
     </comment>
-    <comment ref="A48" authorId="0">
+    <comment ref="A193" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'few'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B193" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'few'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C193" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'few'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D193" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'few'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E193" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'few'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F193" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'few'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G193" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'few'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H193" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'few'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I193" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'few'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A194" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'many'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B194" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'many'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C194" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'many'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D194" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'many'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E194" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'many'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F194" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'many'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G194" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'many'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H194" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'many'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I194" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'many'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A227" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1220,7 +2624,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B48" authorId="0">
+    <comment ref="B227" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1232,7 +2636,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C48" authorId="0">
+    <comment ref="C227" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1244,7 +2648,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D48" authorId="0">
+    <comment ref="D227" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1256,7 +2660,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E48" authorId="0">
+    <comment ref="E227" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1268,7 +2672,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F48" authorId="0">
+    <comment ref="F227" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1280,7 +2684,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G48" authorId="0">
+    <comment ref="G227" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1292,7 +2696,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H48" authorId="0">
+    <comment ref="H227" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1304,7 +2708,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I48" authorId="0">
+    <comment ref="I227" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1316,7 +2720,115 @@
         </r>
       </text>
     </comment>
-    <comment ref="A91" authorId="0">
+    <comment ref="A229" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B229" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C229" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D229" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E229" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F229" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G229" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H229" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I229" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'two'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A230" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1328,7 +2840,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B91" authorId="0">
+    <comment ref="B230" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1340,7 +2852,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C91" authorId="0">
+    <comment ref="C230" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1352,7 +2864,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D91" authorId="0">
+    <comment ref="D230" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1364,7 +2876,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E91" authorId="0">
+    <comment ref="E230" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1376,7 +2888,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F91" authorId="0">
+    <comment ref="F230" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1388,7 +2900,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G91" authorId="0">
+    <comment ref="G230" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1400,7 +2912,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H91" authorId="0">
+    <comment ref="H230" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1412,7 +2924,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I91" authorId="0">
+    <comment ref="I230" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1424,7 +2936,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A92" authorId="0">
+    <comment ref="A231" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1436,7 +2948,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B92" authorId="0">
+    <comment ref="B231" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1448,7 +2960,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C92" authorId="0">
+    <comment ref="C231" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1460,7 +2972,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D92" authorId="0">
+    <comment ref="D231" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1472,7 +2984,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E92" authorId="0">
+    <comment ref="E231" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1484,7 +2996,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F92" authorId="0">
+    <comment ref="F231" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1496,7 +3008,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G92" authorId="0">
+    <comment ref="G231" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1508,7 +3020,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H92" authorId="0">
+    <comment ref="H231" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1520,7 +3032,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I92" authorId="0">
+    <comment ref="I231" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1532,7 +3044,115 @@
         </r>
       </text>
     </comment>
-    <comment ref="A95" authorId="0">
+    <comment ref="A265" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B265" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C265" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D265" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E265" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F265" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G265" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H265" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I265" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12.0"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>The default language does not need/have a translation for the quantity 'zero'.
+If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A267" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1544,7 +3164,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B95" authorId="0">
+    <comment ref="B267" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1556,7 +3176,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C95" authorId="0">
+    <comment ref="C267" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1568,7 +3188,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D95" authorId="0">
+    <comment ref="D267" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1580,7 +3200,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E95" authorId="0">
+    <comment ref="E267" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1592,7 +3212,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F95" authorId="0">
+    <comment ref="F267" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1604,7 +3224,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G95" authorId="0">
+    <comment ref="G267" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1616,7 +3236,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H95" authorId="0">
+    <comment ref="H267" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1628,7 +3248,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I95" authorId="0">
+    <comment ref="I267" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1640,115 +3260,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A96" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B96" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C96" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D96" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E96" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F96" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G96" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H96" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I96" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A147" authorId="0">
+    <comment ref="A268" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1760,7 +3272,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B147" authorId="0">
+    <comment ref="B268" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1772,7 +3284,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C147" authorId="0">
+    <comment ref="C268" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1784,7 +3296,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D147" authorId="0">
+    <comment ref="D268" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1796,7 +3308,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E147" authorId="0">
+    <comment ref="E268" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1808,7 +3320,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F147" authorId="0">
+    <comment ref="F268" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1820,7 +3332,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G147" authorId="0">
+    <comment ref="G268" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1832,7 +3344,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H147" authorId="0">
+    <comment ref="H268" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1844,7 +3356,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I147" authorId="0">
+    <comment ref="I268" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1856,7 +3368,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A148" authorId="0">
+    <comment ref="A269" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1868,7 +3380,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B148" authorId="0">
+    <comment ref="B269" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1880,7 +3392,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C148" authorId="0">
+    <comment ref="C269" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1892,7 +3404,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D148" authorId="0">
+    <comment ref="D269" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1904,7 +3416,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E148" authorId="0">
+    <comment ref="E269" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1916,7 +3428,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F148" authorId="0">
+    <comment ref="F269" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1928,7 +3440,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G148" authorId="0">
+    <comment ref="G269" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1940,7 +3452,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H148" authorId="0">
+    <comment ref="H269" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1952,7 +3464,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I148" authorId="0">
+    <comment ref="I269" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1960,1518 +3472,6 @@
             <rFont val="Calibri"/>
           </rPr>
           <t>The default language does not need/have a translation for the quantity 'many'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A151" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B151" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C151" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D151" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E151" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F151" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G151" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H151" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I151" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A152" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B152" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C152" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D152" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E152" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F152" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G152" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H152" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I152" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A190" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'few'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B190" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'few'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C190" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'few'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D190" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'few'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E190" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'few'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F190" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'few'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G190" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'few'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H190" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'few'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I190" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'few'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A191" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'many'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B191" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'many'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C191" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'many'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D191" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'many'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E191" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'many'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F191" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'many'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G191" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'many'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H191" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'many'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I191" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'many'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A194" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B194" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C194" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D194" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E194" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F194" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G194" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H194" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I194" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A195" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B195" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C195" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D195" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E195" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F195" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G195" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H195" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I195" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A227" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'few'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B227" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'few'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C227" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'few'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D227" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'few'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E227" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'few'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F227" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'few'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G227" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'few'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H227" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'few'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I227" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'few'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A228" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'many'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B228" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'many'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C228" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'many'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D228" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'many'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E228" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'many'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F228" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'many'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G228" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'many'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H228" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'many'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I228" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'many'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A231" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B231" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C231" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D231" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E231" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F231" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G231" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H231" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I231" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A232" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B232" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C232" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D232" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E232" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F232" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G232" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H232" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I232" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A265" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'few'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B265" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'few'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C265" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'few'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D265" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'few'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E265" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'few'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F265" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'few'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G265" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'few'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H265" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'few'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I265" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'few'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A266" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'many'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B266" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'many'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C266" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'many'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D266" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'many'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E266" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'many'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F266" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'many'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G266" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'many'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H266" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'many'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I266" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'many'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A269" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B269" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C269" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D269" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E269" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F269" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G269" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H269" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I269" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'two'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A270" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B270" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C270" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D270" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E270" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F270" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G270" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H270" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
-If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I270" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12.0"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>The default language does not need/have a translation for the quantity 'zero'.
 If this language needs a different translation for this quantity, add it, otherwise ignore this row.</t>
         </r>
       </text>
@@ -3733,24 +3733,30 @@
     <t>已存档</t>
   </si>
   <si>
+    <t>archived_selected_notes_PLURALS_zero</t>
+  </si>
+  <si>
+    <t>archived_selected_notes_PLURALS_one</t>
+  </si>
+  <si>
+    <t>Archived %d note</t>
+  </si>
+  <si>
+    <t>%d note archivée</t>
+  </si>
+  <si>
+    <t>Archiviata %d nota</t>
+  </si>
+  <si>
+    <t>archived_selected_notes_PLURALS_two</t>
+  </si>
+  <si>
     <t>archived_selected_notes_PLURALS_few</t>
   </si>
   <si>
     <t>archived_selected_notes_PLURALS_many</t>
   </si>
   <si>
-    <t>archived_selected_notes_PLURALS_one</t>
-  </si>
-  <si>
-    <t>Archived %d note</t>
-  </si>
-  <si>
-    <t>%d note archivée</t>
-  </si>
-  <si>
-    <t>Archiviata %d nota</t>
-  </si>
-  <si>
     <t>archived_selected_notes_PLURALS_other</t>
   </si>
   <si>
@@ -3763,12 +3769,6 @@
     <t>Archiviate %d note</t>
   </si>
   <si>
-    <t>archived_selected_notes_PLURALS_two</t>
-  </si>
-  <si>
-    <t>archived_selected_notes_PLURALS_zero</t>
-  </si>
-  <si>
     <t>ascending</t>
   </si>
   <si>
@@ -4093,24 +4093,30 @@
     <t>取消</t>
   </si>
   <si>
+    <t>cant_add_files_PLURALS_zero</t>
+  </si>
+  <si>
+    <t>cant_add_files_PLURALS_one</t>
+  </si>
+  <si>
+    <t>Can’t add %d file</t>
+  </si>
+  <si>
+    <t>%d fichier n'a pas pu être ajouté</t>
+  </si>
+  <si>
+    <t>Impossibile aggiungere %d file</t>
+  </si>
+  <si>
+    <t>cant_add_files_PLURALS_two</t>
+  </si>
+  <si>
     <t>cant_add_files_PLURALS_few</t>
   </si>
   <si>
     <t>cant_add_files_PLURALS_many</t>
   </si>
   <si>
-    <t>cant_add_files_PLURALS_one</t>
-  </si>
-  <si>
-    <t>Can’t add %d file</t>
-  </si>
-  <si>
-    <t>%d fichier n'a pas pu être ajouté</t>
-  </si>
-  <si>
-    <t>Impossibile aggiungere %d file</t>
-  </si>
-  <si>
     <t>cant_add_files_PLURALS_other</t>
   </si>
   <si>
@@ -4120,10 +4126,25 @@
     <t>%d fichiers n'ont pas pu être ajoutés</t>
   </si>
   <si>
-    <t>cant_add_files_PLURALS_two</t>
-  </si>
-  <si>
-    <t>cant_add_files_PLURALS_zero</t>
+    <t>cant_add_images_PLURALS_zero</t>
+  </si>
+  <si>
+    <t>cant_add_images_PLURALS_one</t>
+  </si>
+  <si>
+    <t>Can’t add %d image</t>
+  </si>
+  <si>
+    <t>Kann %d Bild nicht hinzufügen</t>
+  </si>
+  <si>
+    <t>Impossible d'ajouter %d image</t>
+  </si>
+  <si>
+    <t>Impossibile aggiungere %d immagine</t>
+  </si>
+  <si>
+    <t>cant_add_images_PLURALS_two</t>
   </si>
   <si>
     <t>cant_add_images_PLURALS_few</t>
@@ -4132,21 +4153,6 @@
     <t>cant_add_images_PLURALS_many</t>
   </si>
   <si>
-    <t>cant_add_images_PLURALS_one</t>
-  </si>
-  <si>
-    <t>Can’t add %d image</t>
-  </si>
-  <si>
-    <t>Kann %d Bild nicht hinzufügen</t>
-  </si>
-  <si>
-    <t>Impossible d'ajouter %d image</t>
-  </si>
-  <si>
-    <t>Impossibile aggiungere %d immagine</t>
-  </si>
-  <si>
     <t>cant_add_images_PLURALS_other</t>
   </si>
   <si>
@@ -4162,12 +4168,6 @@
     <t>Impossibile aggiungere %d immagini</t>
   </si>
   <si>
-    <t>cant_add_images_PLURALS_two</t>
-  </si>
-  <si>
-    <t>cant_add_images_PLURALS_zero</t>
-  </si>
-  <si>
     <t>cant_find_folder</t>
   </si>
   <si>
@@ -4948,24 +4948,30 @@
     <t>已删除</t>
   </si>
   <si>
+    <t>deleted_selected_notes_PLURALS_zero</t>
+  </si>
+  <si>
+    <t>deleted_selected_notes_PLURALS_one</t>
+  </si>
+  <si>
+    <t>Deleted %d note</t>
+  </si>
+  <si>
+    <t>%d note supprimée</t>
+  </si>
+  <si>
+    <t>Eliminata %d nota</t>
+  </si>
+  <si>
+    <t>deleted_selected_notes_PLURALS_two</t>
+  </si>
+  <si>
     <t>deleted_selected_notes_PLURALS_few</t>
   </si>
   <si>
     <t>deleted_selected_notes_PLURALS_many</t>
   </si>
   <si>
-    <t>deleted_selected_notes_PLURALS_one</t>
-  </si>
-  <si>
-    <t>Deleted %d note</t>
-  </si>
-  <si>
-    <t>%d note supprimée</t>
-  </si>
-  <si>
-    <t>Eliminata %d nota</t>
-  </si>
-  <si>
     <t>deleted_selected_notes_PLURALS_other</t>
   </si>
   <si>
@@ -4976,12 +4982,6 @@
   </si>
   <si>
     <t>Eliminate %d note</t>
-  </si>
-  <si>
-    <t>deleted_selected_notes_PLURALS_two</t>
-  </si>
-  <si>
-    <t>deleted_selected_notes_PLURALS_zero</t>
   </si>
   <si>
     <t>deleting_files</t>
@@ -5498,22 +5498,22 @@
     <t>external_data_message</t>
   </si>
   <si>
-    <t>By enabling this, the app’s internal database will be moved into the app’s external storage (Android/media/com.philkes.notallyx).
+    <t>By enabling this, the app’s internal database will be moved into the app’s external storage (Android/media/com.crustack.notallyx).
 In combination with file synchronization apps this can be used to synchronize NotallyX data between multiple devices.</t>
   </si>
   <si>
-    <t>Wird dies aktiviert, wird die app-interne Datenbank in den app-externen Speicher ausgelagert (Android/media/com.philkes.notallyx). In Kombination mit Datei-Synchronisations Apps kann dies genutzt werden um NotallyX Daten zwischen mehrere Geräte zu synchronisieren.</t>
-  </si>
-  <si>
-    <t>En activant cette option, la base de données interne de l'application sera déplacée vers le stockage externe de l'application (Android/media/com.philkes.notallyx).
+    <t>Wird dies aktiviert, wird die app-interne Datenbank in den app-externen Speicher ausgelagert (Android/media/com.crustack.notallyx). In Kombination mit Datei-Synchronisations Apps kann dies genutzt werden um NotallyX Daten zwischen mehrere Geräte zu synchronisieren.</t>
+  </si>
+  <si>
+    <t>En activant cette option, la base de données interne de l'application sera déplacée vers le stockage externe de l'application (Android/media/com.crustack.notallyx).
 En combinaison avec des applications de synchronisation de fichiers, cela peut être utilisé pour synchroniser les données de NotallyX entre plusieurs appareils.</t>
   </si>
   <si>
-    <t>Attivandolo, il database interno dell’app verrà spostato nella memoria esterna dell’app (Android/media/com.philkes.notallyx).
+    <t>Attivandolo, il database interno dell’app verrà spostato nella memoria esterna dell’app (Android/media/com.crustack.notallyx).
 Abbinandolo con un’app di sincronizzazione file potrai così sincronizzare i dati di NotallyX tra dispositivi diversi.</t>
   </si>
   <si>
-    <t>启用此项，应用程序的内部数据库将被移动到应用程序的外部存储（Android / Media / Com.Philkes.notallyX）中。与文件同步应用组合，这可用于同步多个设备之间的数据。</t>
+    <t>启用此项，应用程序的内部数据库将被移动到应用程序的外部存储（Android / Media / Com.Crustack.notallyX）中。与文件同步应用组合，这可用于同步多个设备之间的数据。</t>
   </si>
   <si>
     <t>extracted_files</t>
@@ -5815,24 +5815,30 @@
     <t>Note importate</t>
   </si>
   <si>
+    <t>imported_notes_PLURALS_zero</t>
+  </si>
+  <si>
+    <t>imported_notes_PLURALS_one</t>
+  </si>
+  <si>
+    <t>Imported %s Note</t>
+  </si>
+  <si>
+    <t>%s note importée</t>
+  </si>
+  <si>
+    <t>Importata %s nota</t>
+  </si>
+  <si>
+    <t>imported_notes_PLURALS_two</t>
+  </si>
+  <si>
     <t>imported_notes_PLURALS_few</t>
   </si>
   <si>
     <t>imported_notes_PLURALS_many</t>
   </si>
   <si>
-    <t>imported_notes_PLURALS_one</t>
-  </si>
-  <si>
-    <t>Imported %s Note</t>
-  </si>
-  <si>
-    <t>%s note importée</t>
-  </si>
-  <si>
-    <t>Importata %s nota</t>
-  </si>
-  <si>
     <t>imported_notes_PLURALS_other</t>
   </si>
   <si>
@@ -5845,12 +5851,6 @@
     <t>Importate %s note</t>
   </si>
   <si>
-    <t>imported_notes_PLURALS_two</t>
-  </si>
-  <si>
-    <t>imported_notes_PLURALS_zero</t>
-  </si>
-  <si>
     <t>importing_backup</t>
   </si>
   <si>
@@ -6520,27 +6520,33 @@
     <t>…ancora %d</t>
   </si>
   <si>
+    <t>more_files_PLURALS_zero</t>
+  </si>
+  <si>
+    <t>more_files_PLURALS_one</t>
+  </si>
+  <si>
+    <t>…%d more file</t>
+  </si>
+  <si>
+    <t>…%d weitere Datei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…et %d fichier </t>
+  </si>
+  <si>
+    <t>…%d altro file</t>
+  </si>
+  <si>
+    <t>more_files_PLURALS_two</t>
+  </si>
+  <si>
     <t>more_files_PLURALS_few</t>
   </si>
   <si>
     <t>more_files_PLURALS_many</t>
   </si>
   <si>
-    <t>more_files_PLURALS_one</t>
-  </si>
-  <si>
-    <t>…%d more file</t>
-  </si>
-  <si>
-    <t>…%d weitere Datei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…et %d fichier </t>
-  </si>
-  <si>
-    <t>…%d altro file</t>
-  </si>
-  <si>
     <t>more_files_PLURALS_other</t>
   </si>
   <si>
@@ -6554,12 +6560,6 @@
   </si>
   <si>
     <t>…altri %d file</t>
-  </si>
-  <si>
-    <t>more_files_PLURALS_two</t>
-  </si>
-  <si>
-    <t>more_files_PLURALS_zero</t>
   </si>
   <si>
     <t>next</t>
@@ -7076,24 +7076,30 @@
     <t>恢复</t>
   </si>
   <si>
+    <t>restored_selected_notes_PLURALS_zero</t>
+  </si>
+  <si>
+    <t>restored_selected_notes_PLURALS_one</t>
+  </si>
+  <si>
+    <t>Restored %d note</t>
+  </si>
+  <si>
+    <t>%d note restaurée</t>
+  </si>
+  <si>
+    <t>Ripristinata %d nota</t>
+  </si>
+  <si>
+    <t>restored_selected_notes_PLURALS_two</t>
+  </si>
+  <si>
     <t>restored_selected_notes_PLURALS_few</t>
   </si>
   <si>
     <t>restored_selected_notes_PLURALS_many</t>
   </si>
   <si>
-    <t>restored_selected_notes_PLURALS_one</t>
-  </si>
-  <si>
-    <t>Restored %d note</t>
-  </si>
-  <si>
-    <t>%d note restaurée</t>
-  </si>
-  <si>
-    <t>Ripristinata %d nota</t>
-  </si>
-  <si>
     <t>restored_selected_notes_PLURALS_other</t>
   </si>
   <si>
@@ -7104,12 +7110,6 @@
   </si>
   <si>
     <t>Ripristinate %d note</t>
-  </si>
-  <si>
-    <t>restored_selected_notes_PLURALS_two</t>
-  </si>
-  <si>
-    <t>restored_selected_notes_PLURALS_zero</t>
   </si>
   <si>
     <t>resume</t>
@@ -7710,24 +7710,30 @@
     <t>取消存档</t>
   </si>
   <si>
+    <t>unarchived_selected_notes_PLURALS_zero</t>
+  </si>
+  <si>
+    <t>unarchived_selected_notes_PLURALS_one</t>
+  </si>
+  <si>
+    <t>Unarchived %d note</t>
+  </si>
+  <si>
+    <t>%d note désarchivée</t>
+  </si>
+  <si>
+    <t>Annullata archiviazione di %d nota</t>
+  </si>
+  <si>
+    <t>unarchived_selected_notes_PLURALS_two</t>
+  </si>
+  <si>
     <t>unarchived_selected_notes_PLURALS_few</t>
   </si>
   <si>
     <t>unarchived_selected_notes_PLURALS_many</t>
   </si>
   <si>
-    <t>unarchived_selected_notes_PLURALS_one</t>
-  </si>
-  <si>
-    <t>Unarchived %d note</t>
-  </si>
-  <si>
-    <t>%d note désarchivée</t>
-  </si>
-  <si>
-    <t>Annullata archiviazione di %d nota</t>
-  </si>
-  <si>
     <t>unarchived_selected_notes_PLURALS_other</t>
   </si>
   <si>
@@ -7738,12 +7744,6 @@
   </si>
   <si>
     <t>Annullata archiviazione di %d note</t>
-  </si>
-  <si>
-    <t>unarchived_selected_notes_PLURALS_two</t>
-  </si>
-  <si>
-    <t>unarchived_selected_notes_PLURALS_zero</t>
   </si>
   <si>
     <t>uncheck_all_items</t>
@@ -9630,54 +9630,54 @@
       <c r="B13" t="s" s="1">
         <v>10</v>
       </c>
-      <c r="C13" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="D13" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="E13" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="F13" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="G13" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="H13" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="I13" t="s" s="3">
+      <c r="C13" t="s" s="1">
+        <v>78</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="F13" t="s" s="1">
+        <v>79</v>
+      </c>
+      <c r="G13" t="s" s="1">
+        <v>80</v>
+      </c>
+      <c r="H13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I13" t="s" s="2">
         <v>21</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="1">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B14" t="s" s="1">
         <v>10</v>
       </c>
-      <c r="C14" t="s" s="1">
-        <v>79</v>
-      </c>
-      <c r="D14" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E14" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="F14" t="s" s="1">
-        <v>80</v>
-      </c>
-      <c r="G14" t="s" s="1">
-        <v>81</v>
-      </c>
-      <c r="H14" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I14" t="s" s="2">
+      <c r="C14" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="D14" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="E14" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="F14" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="G14" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="H14" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="I14" t="s" s="3">
         <v>21</v>
       </c>
     </row>
@@ -9688,31 +9688,31 @@
       <c r="B15" t="s" s="1">
         <v>10</v>
       </c>
-      <c r="C15" t="s" s="1">
-        <v>83</v>
-      </c>
-      <c r="D15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="F15" t="s" s="1">
-        <v>84</v>
-      </c>
-      <c r="G15" t="s" s="1">
-        <v>85</v>
-      </c>
-      <c r="H15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I15" t="s" s="2">
+      <c r="C15" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="D15" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="E15" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="F15" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="G15" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="H15" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="I15" t="s" s="3">
         <v>21</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="1">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B16" t="s" s="1">
         <v>10</v>
@@ -9741,30 +9741,30 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="1">
+        <v>84</v>
+      </c>
+      <c r="B17" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="C17" t="s" s="1">
+        <v>85</v>
+      </c>
+      <c r="D17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="F17" t="s" s="1">
+        <v>86</v>
+      </c>
+      <c r="G17" t="s" s="1">
         <v>87</v>
       </c>
-      <c r="B17" t="s" s="1">
-        <v>10</v>
-      </c>
-      <c r="C17" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="D17" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="E17" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="F17" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="G17" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="H17" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="I17" t="s" s="3">
+      <c r="H17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I17" t="s" s="2">
         <v>21</v>
       </c>
     </row>
@@ -10355,54 +10355,54 @@
       <c r="B38" t="s" s="1">
         <v>10</v>
       </c>
-      <c r="C38" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="D38" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="E38" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="F38" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="G38" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="H38" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="I38" t="s" s="3">
+      <c r="C38" t="s" s="1">
+        <v>198</v>
+      </c>
+      <c r="D38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="F38" t="s" s="1">
+        <v>199</v>
+      </c>
+      <c r="G38" t="s" s="1">
+        <v>200</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I38" t="s" s="2">
         <v>21</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="1">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B39" t="s" s="1">
         <v>10</v>
       </c>
-      <c r="C39" t="s" s="1">
-        <v>199</v>
-      </c>
-      <c r="D39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="F39" t="s" s="1">
-        <v>200</v>
-      </c>
-      <c r="G39" t="s" s="1">
-        <v>201</v>
-      </c>
-      <c r="H39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I39" t="s" s="2">
+      <c r="C39" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="D39" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="E39" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="F39" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="G39" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="H39" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="I39" t="s" s="3">
         <v>21</v>
       </c>
     </row>
@@ -10413,31 +10413,31 @@
       <c r="B40" t="s" s="1">
         <v>10</v>
       </c>
-      <c r="C40" t="s" s="1">
-        <v>203</v>
-      </c>
-      <c r="D40" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E40" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="F40" t="s" s="1">
-        <v>204</v>
-      </c>
-      <c r="G40" t="s" s="1">
-        <v>201</v>
-      </c>
-      <c r="H40" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I40" t="s" s="2">
+      <c r="C40" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="D40" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="E40" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="F40" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="G40" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="H40" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="I40" t="s" s="3">
         <v>21</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="1">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B41" t="s" s="1">
         <v>10</v>
@@ -10466,30 +10466,30 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="1">
+        <v>204</v>
+      </c>
+      <c r="B42" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="C42" t="s" s="1">
+        <v>205</v>
+      </c>
+      <c r="D42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="F42" t="s" s="1">
         <v>206</v>
       </c>
-      <c r="B42" t="s" s="1">
-        <v>10</v>
-      </c>
-      <c r="C42" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="D42" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="E42" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="F42" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="G42" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="H42" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="I42" t="s" s="3">
+      <c r="G42" t="s" s="1">
+        <v>200</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I42" t="s" s="2">
         <v>21</v>
       </c>
     </row>
@@ -10529,54 +10529,54 @@
       <c r="B44" t="s" s="1">
         <v>10</v>
       </c>
-      <c r="C44" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="D44" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="E44" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="F44" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="G44" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="H44" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="I44" t="s" s="3">
+      <c r="C44" t="s" s="1">
+        <v>209</v>
+      </c>
+      <c r="D44" t="s" s="1">
+        <v>210</v>
+      </c>
+      <c r="E44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="F44" t="s" s="1">
+        <v>211</v>
+      </c>
+      <c r="G44" t="s" s="1">
+        <v>212</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I44" t="s" s="2">
         <v>21</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="1">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B45" t="s" s="1">
         <v>10</v>
       </c>
-      <c r="C45" t="s" s="1">
-        <v>210</v>
-      </c>
-      <c r="D45" t="s" s="1">
-        <v>211</v>
-      </c>
-      <c r="E45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="F45" t="s" s="1">
-        <v>212</v>
-      </c>
-      <c r="G45" t="s" s="1">
-        <v>213</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I45" t="s" s="2">
+      <c r="C45" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="D45" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="E45" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="F45" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="G45" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="H45" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="I45" t="s" s="3">
         <v>21</v>
       </c>
     </row>
@@ -10587,31 +10587,31 @@
       <c r="B46" t="s" s="1">
         <v>10</v>
       </c>
-      <c r="C46" t="s" s="1">
-        <v>215</v>
-      </c>
-      <c r="D46" t="s" s="1">
-        <v>216</v>
-      </c>
-      <c r="E46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="F46" t="s" s="1">
-        <v>217</v>
-      </c>
-      <c r="G46" t="s" s="1">
-        <v>218</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I46" t="s" s="2">
+      <c r="C46" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="D46" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="E46" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="F46" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="G46" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="H46" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="I46" t="s" s="3">
         <v>21</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="1">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B47" t="s" s="1">
         <v>10</v>
@@ -10640,30 +10640,30 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="1">
+        <v>216</v>
+      </c>
+      <c r="B48" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="C48" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="D48" t="s" s="1">
+        <v>218</v>
+      </c>
+      <c r="E48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="F48" t="s" s="1">
+        <v>219</v>
+      </c>
+      <c r="G48" t="s" s="1">
         <v>220</v>
       </c>
-      <c r="B48" t="s" s="1">
-        <v>10</v>
-      </c>
-      <c r="C48" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="D48" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="E48" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="F48" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="G48" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="H48" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="I48" t="s" s="3">
+      <c r="H48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I48" t="s" s="2">
         <v>21</v>
       </c>
     </row>
@@ -11921,54 +11921,54 @@
       <c r="B92" t="s" s="1">
         <v>10</v>
       </c>
-      <c r="C92" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="D92" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="E92" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="F92" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="G92" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="H92" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="I92" t="s" s="3">
+      <c r="C92" t="s" s="1">
+        <v>483</v>
+      </c>
+      <c r="D92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="F92" t="s" s="1">
+        <v>484</v>
+      </c>
+      <c r="G92" t="s" s="1">
+        <v>485</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I92" t="s" s="2">
         <v>21</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="1">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B93" t="s" s="1">
         <v>10</v>
       </c>
-      <c r="C93" t="s" s="1">
-        <v>484</v>
-      </c>
-      <c r="D93" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E93" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="F93" t="s" s="1">
-        <v>485</v>
-      </c>
-      <c r="G93" t="s" s="1">
-        <v>486</v>
-      </c>
-      <c r="H93" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I93" t="s" s="2">
+      <c r="C93" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="D93" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="E93" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="F93" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="G93" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="H93" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="I93" t="s" s="3">
         <v>21</v>
       </c>
     </row>
@@ -11979,31 +11979,31 @@
       <c r="B94" t="s" s="1">
         <v>10</v>
       </c>
-      <c r="C94" t="s" s="1">
-        <v>488</v>
-      </c>
-      <c r="D94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="F94" t="s" s="1">
-        <v>489</v>
-      </c>
-      <c r="G94" t="s" s="1">
-        <v>490</v>
-      </c>
-      <c r="H94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I94" t="s" s="2">
+      <c r="C94" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="D94" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="E94" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="F94" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="G94" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="H94" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="I94" t="s" s="3">
         <v>21</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="1">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B95" t="s" s="1">
         <v>10</v>
@@ -12032,30 +12032,30 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="1">
+        <v>489</v>
+      </c>
+      <c r="B96" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="C96" t="s" s="1">
+        <v>490</v>
+      </c>
+      <c r="D96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="F96" t="s" s="1">
+        <v>491</v>
+      </c>
+      <c r="G96" t="s" s="1">
         <v>492</v>
       </c>
-      <c r="B96" t="s" s="1">
-        <v>10</v>
-      </c>
-      <c r="C96" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="D96" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="E96" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="F96" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="G96" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="H96" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="I96" t="s" s="3">
+      <c r="H96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I96" t="s" s="2">
         <v>21</v>
       </c>
     </row>
@@ -13545,54 +13545,54 @@
       <c r="B148" t="s" s="1">
         <v>10</v>
       </c>
-      <c r="C148" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="D148" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="E148" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="F148" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="G148" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="H148" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="I148" t="s" s="3">
+      <c r="C148" t="s" s="1">
+        <v>767</v>
+      </c>
+      <c r="D148" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E148" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="F148" t="s" s="1">
+        <v>768</v>
+      </c>
+      <c r="G148" t="s" s="1">
+        <v>769</v>
+      </c>
+      <c r="H148" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I148" t="s" s="2">
         <v>21</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="1">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="B149" t="s" s="1">
         <v>10</v>
       </c>
-      <c r="C149" t="s" s="1">
-        <v>768</v>
-      </c>
-      <c r="D149" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E149" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="F149" t="s" s="1">
-        <v>769</v>
-      </c>
-      <c r="G149" t="s" s="1">
-        <v>770</v>
-      </c>
-      <c r="H149" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I149" t="s" s="2">
+      <c r="C149" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="D149" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="E149" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="F149" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="G149" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="H149" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="I149" t="s" s="3">
         <v>21</v>
       </c>
     </row>
@@ -13603,31 +13603,31 @@
       <c r="B150" t="s" s="1">
         <v>10</v>
       </c>
-      <c r="C150" t="s" s="1">
-        <v>772</v>
-      </c>
-      <c r="D150" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E150" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="F150" t="s" s="1">
-        <v>773</v>
-      </c>
-      <c r="G150" t="s" s="1">
-        <v>774</v>
-      </c>
-      <c r="H150" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I150" t="s" s="2">
+      <c r="C150" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="D150" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="E150" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="F150" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="G150" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="H150" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="I150" t="s" s="3">
         <v>21</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="1">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="B151" t="s" s="1">
         <v>10</v>
@@ -13656,30 +13656,30 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="1">
+        <v>773</v>
+      </c>
+      <c r="B152" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="C152" t="s" s="1">
+        <v>774</v>
+      </c>
+      <c r="D152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="F152" t="s" s="1">
+        <v>775</v>
+      </c>
+      <c r="G152" t="s" s="1">
         <v>776</v>
       </c>
-      <c r="B152" t="s" s="1">
-        <v>10</v>
-      </c>
-      <c r="C152" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="D152" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="E152" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="F152" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="G152" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="H152" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="I152" t="s" s="3">
+      <c r="H152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I152" t="s" s="2">
         <v>21</v>
       </c>
     </row>
@@ -14792,54 +14792,54 @@
       <c r="B191" t="s" s="1">
         <v>10</v>
       </c>
-      <c r="C191" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="D191" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="E191" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="F191" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="G191" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="H191" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="I191" t="s" s="3">
+      <c r="C191" t="s" s="1">
+        <v>1002</v>
+      </c>
+      <c r="D191" t="s" s="1">
+        <v>1003</v>
+      </c>
+      <c r="E191" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="F191" t="s" s="1">
+        <v>1004</v>
+      </c>
+      <c r="G191" t="s" s="1">
+        <v>1005</v>
+      </c>
+      <c r="H191" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I191" t="s" s="2">
         <v>21</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s" s="1">
-        <v>1002</v>
+        <v>1006</v>
       </c>
       <c r="B192" t="s" s="1">
         <v>10</v>
       </c>
-      <c r="C192" t="s" s="1">
-        <v>1003</v>
-      </c>
-      <c r="D192" t="s" s="1">
-        <v>1004</v>
-      </c>
-      <c r="E192" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="F192" t="s" s="1">
-        <v>1005</v>
-      </c>
-      <c r="G192" t="s" s="1">
-        <v>1006</v>
-      </c>
-      <c r="H192" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I192" t="s" s="2">
+      <c r="C192" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="D192" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="E192" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="F192" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="G192" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="H192" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="I192" t="s" s="3">
         <v>21</v>
       </c>
     </row>
@@ -14850,31 +14850,31 @@
       <c r="B193" t="s" s="1">
         <v>10</v>
       </c>
-      <c r="C193" t="s" s="1">
-        <v>1008</v>
-      </c>
-      <c r="D193" t="s" s="1">
-        <v>1009</v>
-      </c>
-      <c r="E193" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="F193" t="s" s="1">
-        <v>1010</v>
-      </c>
-      <c r="G193" t="s" s="1">
-        <v>1011</v>
-      </c>
-      <c r="H193" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I193" t="s" s="2">
+      <c r="C193" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="D193" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="E193" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="F193" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="G193" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="H193" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="I193" t="s" s="3">
         <v>21</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s" s="1">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="B194" t="s" s="1">
         <v>10</v>
@@ -14903,30 +14903,30 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="1">
+        <v>1009</v>
+      </c>
+      <c r="B195" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="C195" t="s" s="1">
+        <v>1010</v>
+      </c>
+      <c r="D195" t="s" s="1">
+        <v>1011</v>
+      </c>
+      <c r="E195" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="F195" t="s" s="1">
+        <v>1012</v>
+      </c>
+      <c r="G195" t="s" s="1">
         <v>1013</v>
       </c>
-      <c r="B195" t="s" s="1">
-        <v>10</v>
-      </c>
-      <c r="C195" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="D195" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="E195" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="F195" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="G195" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="H195" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="I195" t="s" s="3">
+      <c r="H195" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I195" t="s" s="2">
         <v>21</v>
       </c>
     </row>
@@ -15865,54 +15865,54 @@
       <c r="B228" t="s" s="1">
         <v>10</v>
       </c>
-      <c r="C228" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="D228" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="E228" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="F228" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="G228" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="H228" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="I228" t="s" s="3">
+      <c r="C228" t="s" s="1">
+        <v>1185</v>
+      </c>
+      <c r="D228" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E228" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="F228" t="s" s="1">
+        <v>1186</v>
+      </c>
+      <c r="G228" t="s" s="1">
+        <v>1187</v>
+      </c>
+      <c r="H228" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I228" t="s" s="2">
         <v>21</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s" s="1">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="B229" t="s" s="1">
         <v>10</v>
       </c>
-      <c r="C229" t="s" s="1">
-        <v>1186</v>
-      </c>
-      <c r="D229" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E229" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="F229" t="s" s="1">
-        <v>1187</v>
-      </c>
-      <c r="G229" t="s" s="1">
-        <v>1188</v>
-      </c>
-      <c r="H229" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I229" t="s" s="2">
+      <c r="C229" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="D229" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="E229" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="F229" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="G229" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="H229" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="I229" t="s" s="3">
         <v>21</v>
       </c>
     </row>
@@ -15923,31 +15923,31 @@
       <c r="B230" t="s" s="1">
         <v>10</v>
       </c>
-      <c r="C230" t="s" s="1">
-        <v>1190</v>
-      </c>
-      <c r="D230" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E230" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="F230" t="s" s="1">
-        <v>1191</v>
-      </c>
-      <c r="G230" t="s" s="1">
-        <v>1192</v>
-      </c>
-      <c r="H230" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I230" t="s" s="2">
+      <c r="C230" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="D230" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="E230" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="F230" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="G230" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="H230" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="I230" t="s" s="3">
         <v>21</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="s" s="1">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="B231" t="s" s="1">
         <v>10</v>
@@ -15976,30 +15976,30 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="1">
+        <v>1191</v>
+      </c>
+      <c r="B232" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="C232" t="s" s="1">
+        <v>1192</v>
+      </c>
+      <c r="D232" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E232" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="F232" t="s" s="1">
+        <v>1193</v>
+      </c>
+      <c r="G232" t="s" s="1">
         <v>1194</v>
       </c>
-      <c r="B232" t="s" s="1">
-        <v>10</v>
-      </c>
-      <c r="C232" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="D232" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="E232" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="F232" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="G232" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="H232" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="I232" t="s" s="3">
+      <c r="H232" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I232" t="s" s="2">
         <v>21</v>
       </c>
     </row>
@@ -16967,54 +16967,54 @@
       <c r="B266" t="s" s="1">
         <v>10</v>
       </c>
-      <c r="C266" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="D266" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="E266" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="F266" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="G266" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="H266" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="I266" t="s" s="3">
+      <c r="C266" t="s" s="1">
+        <v>1395</v>
+      </c>
+      <c r="D266" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E266" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="F266" t="s" s="1">
+        <v>1396</v>
+      </c>
+      <c r="G266" t="s" s="1">
+        <v>1397</v>
+      </c>
+      <c r="H266" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I266" t="s" s="2">
         <v>21</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="s" s="1">
-        <v>1395</v>
+        <v>1398</v>
       </c>
       <c r="B267" t="s" s="1">
         <v>10</v>
       </c>
-      <c r="C267" t="s" s="1">
-        <v>1396</v>
-      </c>
-      <c r="D267" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E267" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="F267" t="s" s="1">
-        <v>1397</v>
-      </c>
-      <c r="G267" t="s" s="1">
-        <v>1398</v>
-      </c>
-      <c r="H267" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I267" t="s" s="2">
+      <c r="C267" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="D267" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="E267" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="F267" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="G267" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="H267" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="I267" t="s" s="3">
         <v>21</v>
       </c>
     </row>
@@ -17025,31 +17025,31 @@
       <c r="B268" t="s" s="1">
         <v>10</v>
       </c>
-      <c r="C268" t="s" s="1">
-        <v>1400</v>
-      </c>
-      <c r="D268" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E268" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="F268" t="s" s="1">
-        <v>1401</v>
-      </c>
-      <c r="G268" t="s" s="1">
-        <v>1402</v>
-      </c>
-      <c r="H268" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I268" t="s" s="2">
+      <c r="C268" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="D268" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="E268" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="F268" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="G268" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="H268" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="I268" t="s" s="3">
         <v>21</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="s" s="1">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="B269" t="s" s="1">
         <v>10</v>
@@ -17078,30 +17078,30 @@
     </row>
     <row r="270">
       <c r="A270" t="s" s="1">
+        <v>1401</v>
+      </c>
+      <c r="B270" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="C270" t="s" s="1">
+        <v>1402</v>
+      </c>
+      <c r="D270" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E270" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="F270" t="s" s="1">
+        <v>1403</v>
+      </c>
+      <c r="G270" t="s" s="1">
         <v>1404</v>
       </c>
-      <c r="B270" t="s" s="1">
-        <v>10</v>
-      </c>
-      <c r="C270" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="D270" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="E270" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="F270" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="G270" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="H270" t="s" s="3">
-        <v>21</v>
-      </c>
-      <c r="I270" t="s" s="3">
+      <c r="H270" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I270" t="s" s="2">
         <v>21</v>
       </c>
     </row>
